--- a/data/device_properties/ibm/ibm_fez/ibm_fez_2025-11-30.xlsx
+++ b/data/device_properties/ibm/ibm_fez/ibm_fez_2025-11-30.xlsx
@@ -10,7 +10,6 @@
     <sheet name="basic_info" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="gate_info" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="qubit_info" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="general_info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +451,11 @@
           <t>last_update_date</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>coupling_map</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,6 +476,11 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>2025-11-29T23:51:51+08:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[[0, 1], [1, 0], [1, 2], [2, 1], [2, 3], [3, 2], [3, 4], [3, 16], [4, 3], [4, 5], [5, 4], [5, 6], [6, 5], [6, 7], [7, 6], [7, 8], [7, 17], [8, 7], [8, 9], [9, 8], [9, 10], [10, 9], [10, 11], [11, 10], [11, 12], [11, 18], [12, 11], [12, 13], [13, 12], [13, 14], [14, 13], [14, 15], [15, 14], [15, 19], [16, 3], [16, 23], [17, 7], [17, 27], [18, 11], [18, 31], [19, 15], [19, 35], [20, 21], [21, 20], [21, 22], [21, 36], [22, 21], [22, 23], [23, 16], [23, 22], [23, 24], [24, 23], [24, 25], [25, 24], [25, 26], [25, 37], [26, 25], [26, 27], [27, 17], [27, 26], [27, 28], [28, 27], [28, 29], [29, 28], [29, 30], [29, 38], [30, 29], [30, 31], [31, 18], [31, 30], [31, 32], [32, 31], [32, 33], [33, 32], [33, 34], [33, 39], [34, 33], [34, 35], [35, 19], [35, 34], [36, 21], [36, 41], [37, 25], [37, 45], [38, 29], [38, 49], [39, 33], [39, 53], [40, 41], [41, 36], [41, 40], [41, 42], [42, 41], [42, 43], [43, 42], [43, 44], [43, 56], [44, 43], [44, 45], [45, 37], [45, 44], [45, 46], [46, 45], [46, 47], [47, 46], [47, 48], [47, 57], [48, 47], [48, 49], [49, 38], [49, 48], [49, 50], [50, 49], [50, 51], [51, 50], [51, 52], [51, 58], [52, 51], [52, 53], [53, 39], [53, 52], [53, 54], [54, 53], [54, 55], [55, 54], [55, 59], [56, 43], [56, 63], [57, 47], [57, 67], [58, 51], [58, 71], [59, 55], [59, 75], [60, 61], [61, 60], [61, 62], [61, 76], [62, 61], [62, 63], [63, 56], [63, 62], [63, 64], [64, 63], [64, 65], [65, 64], [65, 66], [65, 77], [66, 65], [66, 67], [67, 57], [67, 66], [67, 68], [68, 67], [68, 69], [69, 68], [69, 70], [69, 78], [70, 69], [70, 71], [71, 58], [71, 70], [71, 72], [72, 71], [72, 73], [73, 72], [73, 74], [73, 79], [74, 73], [74, 75], [75, 59], [75, 74], [76, 61], [76, 81], [77, 65], [77, 85], [78, 69], [78, 89], [79, 73], [79, 93], [80, 81], [81, 76], [81, 80], [81, 82], [82, 81], [82, 83], [83, 82], [83, 84], [83, 96], [84, 83], [84, 85], [85, 77], [85, 84], [85, 86], [86, 85], [86, 87], [87, 86], [87, 88], [87, 97], [88, 87], [88, 89], [89, 78], [89, 88], [89, 90], [90, 89], [90, 91], [91, 90], [91, 92], [91, 98], [92, 91], [92, 93], [93, 79], [93, 92], [93, 94], [94, 93], [94, 95], [95, 94], [95, 99], [96, 83], [96, 103], [97, 87], [97, 107], [98, 91], [98, 111], [99, 95], [99, 115], [100, 101], [101, 100], [101, 102], [101, 116], [102, 101], [102, 103], [103, 96], [103, 102], [103, 104], [104, 103], [104, 105], [105, 104], [105, 106], [105, 117], [106, 105], [106, 107], [107, 97], [107, 106], [107, 108], [108, 107], [108, 109], [109, 108], [109, 110], [109, 118], [110, 109], [110, 111], [111, 98], [111, 110], [111, 112], [112, 111], [112, 113], [113, 112], [113, 114], [113, 119], [114, 113], [114, 115], [115, 99], [115, 114], [116, 101], [116, 121], [117, 105], [117, 125], [118, 109], [118, 129], [119, 113], [119, 133], [120, 121], [121, 116], [121, 120], [121, 122], [122, 121], [122, 123], [123, 122], [123, 124], [123, 136], [124, 123], [124, 125], [125, 117], [125, 124], [125, 126], [126, 125], [126, 127], [127, 126], [127, 128], [127, 137], [128, 127], [128, 129], [129, 118], [129, 128], [129, 130], [130, 129], [130, 131], [131, 130], [131, 132], [131, 138], [132, 131], [132, 133], [133, 119], [133, 132], [133, 134], [134, 133], [134, 135], [135, 134], [135, 139], [136, 123], [136, 143], [137, 127], [137, 147], [138, 131], [138, 151], [139, 135], [139, 155], [140, 141], [141, 140], [141, 142], [142, 141], [142, 143], [143, 136], [143, 142], [143, 144], [144, 143], [144, 145], [145, 144], [145, 146], [146, 145], [146, 147], [147, 137], [147, 146], [147, 148], [148, 147], [148, 149], [149, 148], [149, 150], [150, 149], [150, 151], [151, 138], [151, 150], [151, 152], [152, 151], [152, 153], [153, 152], [153, 154], [154, 153], [154, 155], [155, 139], [155, 154]]</t>
         </is>
       </c>
     </row>
@@ -80834,8632 +80843,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D450"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>jq_7273</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>zz_7273</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>jq_717</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>zz_717</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>jq_6768</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>zz_6768</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>jq_4445</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>zz_4445</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>jq_89</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>zz_89</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>jq_4041</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>zz_4041</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>jq_100101</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>zz_100101</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>jq_9198</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>zz_9198</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>jq_132133</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>zz_132133</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>jq_4142</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>zz_4142</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>jq_5559</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>zz_5559</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>jq_7374</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>zz_7374</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>jq_133134</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>zz_133134</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>jq_5975</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>zz_5975</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>jq_1415</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>zz_1415</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>jq_910</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>zz_910</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>jq_7475</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>zz_7475</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>jq_3953</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>zz_3953</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>jq_129130</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>zz_129130</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>jq_106107</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>zz_106107</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>jq_8396</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>zz_8396</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>jq_111112</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>zz_111112</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>jq_138151</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>zz_138151</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>jq_4748</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>zz_4748</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>jq_4243</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>zz_4243</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>jq_4757</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>zz_4757</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>jq_107108</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>zz_107108</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>jq_134135</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>zz_134135</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>jq_144145</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>zz_144145</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>jq_4849</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>zz_4849</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>jq_7785</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>zz_7785</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>jq_103104</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>zz_103104</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>0</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>jq_8081</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>zz_8081</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>jq_8586</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>zz_8586</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>jq_131138</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>zz_131138</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>jq_140141</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>zz_140141</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>jq_3641</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>zz_3641</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>jq_7172</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>zz_7172</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>jq_8182</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>zz_8182</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>jq_108109</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>zz_108109</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>jq_1213</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>zz_1213</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>jq_99115</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>zz_99115</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>jq_2223</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>zz_2223</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>jq_2938</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>zz_2938</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>jq_4950</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>zz_4950</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>jq_104105</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>zz_104105</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>jq_114115</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>zz_114115</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>jq_109110</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>zz_109110</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>jq_1314</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>zz_1314</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>jq_123136</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>zz_123136</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>0</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>jq_151152</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>zz_151152</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>jq_4546</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>zz_4546</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>jq_110111</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>zz_110111</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>0</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>jq_5051</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>0</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>zz_5051</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>0</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>jq_96103</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>0</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>zz_96103</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>jq_105106</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>zz_105106</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>jq_8283</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>zz_8283</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>jq_147148</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>zz_147148</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>jq_137147</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>0</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>zz_137147</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>jq_5152</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>zz_5152</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>jq_142143</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>zz_142143</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>jq_4647</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>zz_4647</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>jq_2324</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>zz_2324</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>jq_143144</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>zz_143144</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>jq_2136</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>zz_2136</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>jq_8384</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>0</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>zz_8384</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>0</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>jq_113119</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>0</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>zz_113119</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>0</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>jq_7681</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>0</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>zz_7681</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>jq_2425</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>0</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>zz_2425</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>jq_105117</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>0</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>zz_105117</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>0</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>jq_2021</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>0</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>zz_2021</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>0</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>jq_5253</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>zz_5253</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>0</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>jq_139155</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>0</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>zz_139155</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>0</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>jq_6978</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>0</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>zz_6978</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>0</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>jq_112113</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>0</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>zz_112113</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>jq_8990</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>zz_8990</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>0</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>jq_149150</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>zz_149150</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>0</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>jq_5354</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>0</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>zz_5354</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>0</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>jq_1118</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>0</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>zz_1118</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>0</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>jq_3031</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>0</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>zz_3031</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>0</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>jq_2526</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>0</v>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>zz_2526</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>0</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>jq_1623</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>0</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>zz_1623</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>0</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>jq_9091</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>0</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>zz_9091</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>0</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>jq_136143</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>0</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>zz_136143</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>0</v>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>jq_145146</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>0</v>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>zz_145146</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>0</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>jq_2627</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>0</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>zz_2627</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>0</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>jq_2122</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>0</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>zz_2122</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>0</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>jq_316</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>0</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>zz_316</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>0</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>jq_3132</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>0</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>zz_3132</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>0</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>jq_5871</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>0</v>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>zz_5871</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>0</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>jq_8687</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>0</v>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>zz_8687</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>0</v>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>jq_141142</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>0</v>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>zz_141142</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>0</v>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>jq_9599</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>0</v>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>zz_9599</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>0</v>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>jq_6176</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>0</v>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>zz_6176</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>0</v>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>jq_113114</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>0</v>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>zz_113114</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>0</v>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>jq_123124</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>0</v>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>zz_123124</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>0</v>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>jq_2728</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>0</v>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>zz_2728</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>0</v>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>jq_1727</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>0</v>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>zz_1727</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>0</v>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>jq_5455</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>0</v>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>zz_5455</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>0</v>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>jq_6465</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>0</v>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>zz_6465</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>0</v>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>jq_146147</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>0</v>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>zz_146147</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>0</v>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>jq_56</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>0</v>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>zz_56</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>0</v>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>jq_5158</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>0</v>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>zz_5158</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>0</v>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>jq_6061</t>
-        </is>
-      </c>
-      <c r="B208" t="n">
-        <v>0</v>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>zz_6061</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>0</v>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>jq_8788</t>
-        </is>
-      </c>
-      <c r="B210" t="n">
-        <v>0</v>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>zz_8788</t>
-        </is>
-      </c>
-      <c r="B211" t="n">
-        <v>0</v>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>jq_3849</t>
-        </is>
-      </c>
-      <c r="B212" t="n">
-        <v>0</v>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>zz_3849</t>
-        </is>
-      </c>
-      <c r="B213" t="n">
-        <v>0</v>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>jq_152153</t>
-        </is>
-      </c>
-      <c r="B214" t="n">
-        <v>0</v>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>zz_152153</t>
-        </is>
-      </c>
-      <c r="B215" t="n">
-        <v>0</v>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>jq_8797</t>
-        </is>
-      </c>
-      <c r="B216" t="n">
-        <v>0</v>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>zz_8797</t>
-        </is>
-      </c>
-      <c r="B217" t="n">
-        <v>0</v>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>jq_12</t>
-        </is>
-      </c>
-      <c r="B218" t="n">
-        <v>0</v>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>zz_12</t>
-        </is>
-      </c>
-      <c r="B219" t="n">
-        <v>0</v>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>jq_2829</t>
-        </is>
-      </c>
-      <c r="B220" t="n">
-        <v>0</v>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>zz_2829</t>
-        </is>
-      </c>
-      <c r="B221" t="n">
-        <v>0</v>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>jq_9394</t>
-        </is>
-      </c>
-      <c r="B222" t="n">
-        <v>0</v>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>zz_9394</t>
-        </is>
-      </c>
-      <c r="B223" t="n">
-        <v>0</v>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>jq_148149</t>
-        </is>
-      </c>
-      <c r="B224" t="n">
-        <v>0</v>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>zz_148149</t>
-        </is>
-      </c>
-      <c r="B225" t="n">
-        <v>0</v>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>jq_1935</t>
-        </is>
-      </c>
-      <c r="B226" t="n">
-        <v>0</v>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>zz_1935</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>0</v>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>jq_8889</t>
-        </is>
-      </c>
-      <c r="B228" t="n">
-        <v>0</v>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>zz_8889</t>
-        </is>
-      </c>
-      <c r="B229" t="n">
-        <v>0</v>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>jq_117125</t>
-        </is>
-      </c>
-      <c r="B230" t="n">
-        <v>0</v>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>zz_117125</t>
-        </is>
-      </c>
-      <c r="B231" t="n">
-        <v>0</v>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>jq_120121</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>0</v>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>zz_120121</t>
-        </is>
-      </c>
-      <c r="B233" t="n">
-        <v>0</v>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>jq_5663</t>
-        </is>
-      </c>
-      <c r="B234" t="n">
-        <v>0</v>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>zz_5663</t>
-        </is>
-      </c>
-      <c r="B235" t="n">
-        <v>0</v>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>jq_2930</t>
-        </is>
-      </c>
-      <c r="B236" t="n">
-        <v>0</v>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>zz_2930</t>
-        </is>
-      </c>
-      <c r="B237" t="n">
-        <v>0</v>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>jq_8485</t>
-        </is>
-      </c>
-      <c r="B238" t="n">
-        <v>0</v>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>zz_8485</t>
-        </is>
-      </c>
-      <c r="B239" t="n">
-        <v>0</v>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>jq_6162</t>
-        </is>
-      </c>
-      <c r="B240" t="n">
-        <v>0</v>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>zz_6162</t>
-        </is>
-      </c>
-      <c r="B241" t="n">
-        <v>0</v>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>jq_4356</t>
-        </is>
-      </c>
-      <c r="B242" t="n">
-        <v>0</v>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>zz_4356</t>
-        </is>
-      </c>
-      <c r="B243" t="n">
-        <v>0</v>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>jq_98111</t>
-        </is>
-      </c>
-      <c r="B244" t="n">
-        <v>0</v>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>zz_98111</t>
-        </is>
-      </c>
-      <c r="B245" t="n">
-        <v>0</v>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>jq_126127</t>
-        </is>
-      </c>
-      <c r="B246" t="n">
-        <v>0</v>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>zz_126127</t>
-        </is>
-      </c>
-      <c r="B247" t="n">
-        <v>0</v>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>jq_121122</t>
-        </is>
-      </c>
-      <c r="B248" t="n">
-        <v>0</v>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>zz_121122</t>
-        </is>
-      </c>
-      <c r="B249" t="n">
-        <v>0</v>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>jq_135139</t>
-        </is>
-      </c>
-      <c r="B250" t="n">
-        <v>0</v>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>zz_135139</t>
-        </is>
-      </c>
-      <c r="B251" t="n">
-        <v>0</v>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>jq_101116</t>
-        </is>
-      </c>
-      <c r="B252" t="n">
-        <v>0</v>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>zz_101116</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>0</v>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>jq_153154</t>
-        </is>
-      </c>
-      <c r="B254" t="n">
-        <v>0</v>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>zz_153154</t>
-        </is>
-      </c>
-      <c r="B255" t="n">
-        <v>0</v>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>jq_23</t>
-        </is>
-      </c>
-      <c r="B256" t="n">
-        <v>0</v>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>zz_23</t>
-        </is>
-      </c>
-      <c r="B257" t="n">
-        <v>0</v>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>jq_122123</t>
-        </is>
-      </c>
-      <c r="B258" t="n">
-        <v>0</v>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>zz_122123</t>
-        </is>
-      </c>
-      <c r="B259" t="n">
-        <v>0</v>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>jq_5767</t>
-        </is>
-      </c>
-      <c r="B260" t="n">
-        <v>0</v>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>zz_5767</t>
-        </is>
-      </c>
-      <c r="B261" t="n">
-        <v>0</v>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>jq_6263</t>
-        </is>
-      </c>
-      <c r="B262" t="n">
-        <v>0</v>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>zz_6263</t>
-        </is>
-      </c>
-      <c r="B263" t="n">
-        <v>0</v>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>jq_9495</t>
-        </is>
-      </c>
-      <c r="B264" t="n">
-        <v>0</v>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>zz_9495</t>
-        </is>
-      </c>
-      <c r="B265" t="n">
-        <v>0</v>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>jq_154155</t>
-        </is>
-      </c>
-      <c r="B266" t="n">
-        <v>0</v>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>zz_154155</t>
-        </is>
-      </c>
-      <c r="B267" t="n">
-        <v>0</v>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>jq_119133</t>
-        </is>
-      </c>
-      <c r="B268" t="n">
-        <v>0</v>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>zz_119133</t>
-        </is>
-      </c>
-      <c r="B269" t="n">
-        <v>0</v>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>jq_34</t>
-        </is>
-      </c>
-      <c r="B270" t="n">
-        <v>0</v>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>zz_34</t>
-        </is>
-      </c>
-      <c r="B271" t="n">
-        <v>0</v>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>jq_3339</t>
-        </is>
-      </c>
-      <c r="B272" t="n">
-        <v>0</v>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>zz_3339</t>
-        </is>
-      </c>
-      <c r="B273" t="n">
-        <v>0</v>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>jq_150151</t>
-        </is>
-      </c>
-      <c r="B274" t="n">
-        <v>0</v>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>zz_150151</t>
-        </is>
-      </c>
-      <c r="B275" t="n">
-        <v>0</v>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>jq_127128</t>
-        </is>
-      </c>
-      <c r="B276" t="n">
-        <v>0</v>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>zz_127128</t>
-        </is>
-      </c>
-      <c r="B277" t="n">
-        <v>0</v>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>jq_7889</t>
-        </is>
-      </c>
-      <c r="B278" t="n">
-        <v>0</v>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>zz_7889</t>
-        </is>
-      </c>
-      <c r="B279" t="n">
-        <v>0</v>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>jq_127137</t>
-        </is>
-      </c>
-      <c r="B280" t="n">
-        <v>0</v>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>zz_127137</t>
-        </is>
-      </c>
-      <c r="B281" t="n">
-        <v>0</v>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>jq_9192</t>
-        </is>
-      </c>
-      <c r="B282" t="n">
-        <v>0</v>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>zz_9192</t>
-        </is>
-      </c>
-      <c r="B283" t="n">
-        <v>0</v>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>jq_6869</t>
-        </is>
-      </c>
-      <c r="B284" t="n">
-        <v>0</v>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>zz_6869</t>
-        </is>
-      </c>
-      <c r="B285" t="n">
-        <v>0</v>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>jq_3745</t>
-        </is>
-      </c>
-      <c r="B286" t="n">
-        <v>0</v>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>zz_3745</t>
-        </is>
-      </c>
-      <c r="B287" t="n">
-        <v>0</v>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>jq_6364</t>
-        </is>
-      </c>
-      <c r="B288" t="n">
-        <v>0</v>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>zz_6364</t>
-        </is>
-      </c>
-      <c r="B289" t="n">
-        <v>0</v>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>jq_128129</t>
-        </is>
-      </c>
-      <c r="B290" t="n">
-        <v>0</v>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>zz_128129</t>
-        </is>
-      </c>
-      <c r="B291" t="n">
-        <v>0</v>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>jq_3233</t>
-        </is>
-      </c>
-      <c r="B292" t="n">
-        <v>0</v>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>zz_3233</t>
-        </is>
-      </c>
-      <c r="B293" t="n">
-        <v>0</v>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>jq_45</t>
-        </is>
-      </c>
-      <c r="B294" t="n">
-        <v>0</v>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>zz_45</t>
-        </is>
-      </c>
-      <c r="B295" t="n">
-        <v>0</v>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>jq_7993</t>
-        </is>
-      </c>
-      <c r="B296" t="n">
-        <v>0</v>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>zz_7993</t>
-        </is>
-      </c>
-      <c r="B297" t="n">
-        <v>0</v>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>jq_2537</t>
-        </is>
-      </c>
-      <c r="B298" t="n">
-        <v>0</v>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>zz_2537</t>
-        </is>
-      </c>
-      <c r="B299" t="n">
-        <v>0</v>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>jq_6970</t>
-        </is>
-      </c>
-      <c r="B300" t="n">
-        <v>0</v>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>zz_6970</t>
-        </is>
-      </c>
-      <c r="B301" t="n">
-        <v>0</v>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>jq_1831</t>
-        </is>
-      </c>
-      <c r="B302" t="n">
-        <v>0</v>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>zz_1831</t>
-        </is>
-      </c>
-      <c r="B303" t="n">
-        <v>0</v>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>jq_101102</t>
-        </is>
-      </c>
-      <c r="B304" t="n">
-        <v>0</v>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>zz_101102</t>
-        </is>
-      </c>
-      <c r="B305" t="n">
-        <v>0</v>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>jq_116121</t>
-        </is>
-      </c>
-      <c r="B306" t="n">
-        <v>0</v>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>zz_116121</t>
-        </is>
-      </c>
-      <c r="B307" t="n">
-        <v>0</v>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>jq_124125</t>
-        </is>
-      </c>
-      <c r="B308" t="n">
-        <v>0</v>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>zz_124125</t>
-        </is>
-      </c>
-      <c r="B309" t="n">
-        <v>0</v>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>jq_01</t>
-        </is>
-      </c>
-      <c r="B310" t="n">
-        <v>0</v>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>zz_01</t>
-        </is>
-      </c>
-      <c r="B311" t="n">
-        <v>0</v>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>jq_1011</t>
-        </is>
-      </c>
-      <c r="B312" t="n">
-        <v>0</v>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>zz_1011</t>
-        </is>
-      </c>
-      <c r="B313" t="n">
-        <v>0</v>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>jq_6566</t>
-        </is>
-      </c>
-      <c r="B314" t="n">
-        <v>0</v>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>zz_6566</t>
-        </is>
-      </c>
-      <c r="B315" t="n">
-        <v>0</v>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>jq_9293</t>
-        </is>
-      </c>
-      <c r="B316" t="n">
-        <v>0</v>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>zz_9293</t>
-        </is>
-      </c>
-      <c r="B317" t="n">
-        <v>0</v>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>jq_97107</t>
-        </is>
-      </c>
-      <c r="B318" t="n">
-        <v>0</v>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>zz_97107</t>
-        </is>
-      </c>
-      <c r="B319" t="n">
-        <v>0</v>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>jq_102103</t>
-        </is>
-      </c>
-      <c r="B320" t="n">
-        <v>0</v>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>zz_102103</t>
-        </is>
-      </c>
-      <c r="B321" t="n">
-        <v>0</v>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>jq_109118</t>
-        </is>
-      </c>
-      <c r="B322" t="n">
-        <v>0</v>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>zz_109118</t>
-        </is>
-      </c>
-      <c r="B323" t="n">
-        <v>0</v>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>jq_67</t>
-        </is>
-      </c>
-      <c r="B324" t="n">
-        <v>0</v>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>zz_67</t>
-        </is>
-      </c>
-      <c r="B325" t="n">
-        <v>0</v>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>jq_1519</t>
-        </is>
-      </c>
-      <c r="B326" t="n">
-        <v>0</v>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>zz_1519</t>
-        </is>
-      </c>
-      <c r="B327" t="n">
-        <v>0</v>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>jq_3334</t>
-        </is>
-      </c>
-      <c r="B328" t="n">
-        <v>0</v>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>zz_3334</t>
-        </is>
-      </c>
-      <c r="B329" t="n">
-        <v>0</v>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>jq_4344</t>
-        </is>
-      </c>
-      <c r="B330" t="n">
-        <v>0</v>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>zz_4344</t>
-        </is>
-      </c>
-      <c r="B331" t="n">
-        <v>0</v>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>jq_7379</t>
-        </is>
-      </c>
-      <c r="B332" t="n">
-        <v>0</v>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>zz_7379</t>
-        </is>
-      </c>
-      <c r="B333" t="n">
-        <v>0</v>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>jq_7071</t>
-        </is>
-      </c>
-      <c r="B334" t="n">
-        <v>0</v>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>zz_7071</t>
-        </is>
-      </c>
-      <c r="B335" t="n">
-        <v>0</v>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>jq_125126</t>
-        </is>
-      </c>
-      <c r="B336" t="n">
-        <v>0</v>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>zz_125126</t>
-        </is>
-      </c>
-      <c r="B337" t="n">
-        <v>0</v>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>jq_118129</t>
-        </is>
-      </c>
-      <c r="B338" t="n">
-        <v>0</v>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>zz_118129</t>
-        </is>
-      </c>
-      <c r="B339" t="n">
-        <v>0</v>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>jq_130131</t>
-        </is>
-      </c>
-      <c r="B340" t="n">
-        <v>0</v>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>zz_130131</t>
-        </is>
-      </c>
-      <c r="B341" t="n">
-        <v>0</v>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>jq_3435</t>
-        </is>
-      </c>
-      <c r="B342" t="n">
-        <v>0</v>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>zz_3435</t>
-        </is>
-      </c>
-      <c r="B343" t="n">
-        <v>0</v>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>jq_1112</t>
-        </is>
-      </c>
-      <c r="B344" t="n">
-        <v>0</v>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>zz_1112</t>
-        </is>
-      </c>
-      <c r="B345" t="n">
-        <v>0</v>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>jq_6667</t>
-        </is>
-      </c>
-      <c r="B346" t="n">
-        <v>0</v>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>zz_6667</t>
-        </is>
-      </c>
-      <c r="B347" t="n">
-        <v>0</v>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>jq_6577</t>
-        </is>
-      </c>
-      <c r="B348" t="n">
-        <v>0</v>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>zz_6577</t>
-        </is>
-      </c>
-      <c r="B349" t="n">
-        <v>0</v>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>jq_131132</t>
-        </is>
-      </c>
-      <c r="B350" t="n">
-        <v>0</v>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>zz_131132</t>
-        </is>
-      </c>
-      <c r="B351" t="n">
-        <v>0</v>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>jq_78</t>
-        </is>
-      </c>
-      <c r="B352" t="n">
-        <v>0</v>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>zz_78</t>
-        </is>
-      </c>
-      <c r="B353" t="n">
-        <v>0</v>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>GHz</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>2025-11-29T23:51:51+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>lf_4</t>
-        </is>
-      </c>
-      <c r="B354" t="n">
-        <v>0.9890792780146014</v>
-      </c>
-      <c r="C354" t="inlineStr"/>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>lf_5</t>
-        </is>
-      </c>
-      <c r="B355" t="n">
-        <v>0.985241106543801</v>
-      </c>
-      <c r="C355" t="inlineStr"/>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>lf_6</t>
-        </is>
-      </c>
-      <c r="B356" t="n">
-        <v>0.9812705047034765</v>
-      </c>
-      <c r="C356" t="inlineStr"/>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>lf_7</t>
-        </is>
-      </c>
-      <c r="B357" t="n">
-        <v>0.9775389204603243</v>
-      </c>
-      <c r="C357" t="inlineStr"/>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>lf_8</t>
-        </is>
-      </c>
-      <c r="B358" t="n">
-        <v>0.9739658477785358</v>
-      </c>
-      <c r="C358" t="inlineStr"/>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>lf_9</t>
-        </is>
-      </c>
-      <c r="B359" t="n">
-        <v>0.9703094014952923</v>
-      </c>
-      <c r="C359" t="inlineStr"/>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>lf_10</t>
-        </is>
-      </c>
-      <c r="B360" t="n">
-        <v>0.9665440674665132</v>
-      </c>
-      <c r="C360" t="inlineStr"/>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>lf_11</t>
-        </is>
-      </c>
-      <c r="B361" t="n">
-        <v>0.9622710142593219</v>
-      </c>
-      <c r="C361" t="inlineStr"/>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>lf_12</t>
-        </is>
-      </c>
-      <c r="B362" t="n">
-        <v>0.957813299782081</v>
-      </c>
-      <c r="C362" t="inlineStr"/>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>lf_13</t>
-        </is>
-      </c>
-      <c r="B363" t="n">
-        <v>0.9522402229543629</v>
-      </c>
-      <c r="C363" t="inlineStr"/>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>lf_14</t>
-        </is>
-      </c>
-      <c r="B364" t="n">
-        <v>0.945299942477824</v>
-      </c>
-      <c r="C364" t="inlineStr"/>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>lf_15</t>
-        </is>
-      </c>
-      <c r="B365" t="n">
-        <v>0.9386105759105238</v>
-      </c>
-      <c r="C365" t="inlineStr"/>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>lf_16</t>
-        </is>
-      </c>
-      <c r="B366" t="n">
-        <v>0.9338696095667496</v>
-      </c>
-      <c r="C366" t="inlineStr"/>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>lf_17</t>
-        </is>
-      </c>
-      <c r="B367" t="n">
-        <v>0.9292395392860324</v>
-      </c>
-      <c r="C367" t="inlineStr"/>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>lf_18</t>
-        </is>
-      </c>
-      <c r="B368" t="n">
-        <v>0.9254032666764398</v>
-      </c>
-      <c r="C368" t="inlineStr"/>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>lf_19</t>
-        </is>
-      </c>
-      <c r="B369" t="n">
-        <v>0.9211452380023087</v>
-      </c>
-      <c r="C369" t="inlineStr"/>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>lf_20</t>
-        </is>
-      </c>
-      <c r="B370" t="n">
-        <v>0.9168780384273064</v>
-      </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>lf_21</t>
-        </is>
-      </c>
-      <c r="B371" t="n">
-        <v>0.9123625378406423</v>
-      </c>
-      <c r="C371" t="inlineStr"/>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>lf_22</t>
-        </is>
-      </c>
-      <c r="B372" t="n">
-        <v>0.9076891703772025</v>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>lf_23</t>
-        </is>
-      </c>
-      <c r="B373" t="n">
-        <v>0.902829049611328</v>
-      </c>
-      <c r="C373" t="inlineStr"/>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>lf_24</t>
-        </is>
-      </c>
-      <c r="B374" t="n">
-        <v>0.897693709717599</v>
-      </c>
-      <c r="C374" t="inlineStr"/>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>lf_25</t>
-        </is>
-      </c>
-      <c r="B375" t="n">
-        <v>0.8926717361550368</v>
-      </c>
-      <c r="C375" t="inlineStr"/>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>lf_26</t>
-        </is>
-      </c>
-      <c r="B376" t="n">
-        <v>0.8883165856199101</v>
-      </c>
-      <c r="C376" t="inlineStr"/>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>lf_27</t>
-        </is>
-      </c>
-      <c r="B377" t="n">
-        <v>0.8842491254854926</v>
-      </c>
-      <c r="C377" t="inlineStr"/>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>lf_28</t>
-        </is>
-      </c>
-      <c r="B378" t="n">
-        <v>0.8785220380691486</v>
-      </c>
-      <c r="C378" t="inlineStr"/>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>lf_29</t>
-        </is>
-      </c>
-      <c r="B379" t="n">
-        <v>0.8724869655038197</v>
-      </c>
-      <c r="C379" t="inlineStr"/>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>lf_30</t>
-        </is>
-      </c>
-      <c r="B380" t="n">
-        <v>0.8684057736720557</v>
-      </c>
-      <c r="C380" t="inlineStr"/>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>lf_31</t>
-        </is>
-      </c>
-      <c r="B381" t="n">
-        <v>0.8642058301504169</v>
-      </c>
-      <c r="C381" t="inlineStr"/>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>lf_32</t>
-        </is>
-      </c>
-      <c r="B382" t="n">
-        <v>0.8602559088631847</v>
-      </c>
-      <c r="C382" t="inlineStr"/>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>lf_33</t>
-        </is>
-      </c>
-      <c r="B383" t="n">
-        <v>0.8546842202423101</v>
-      </c>
-      <c r="C383" t="inlineStr"/>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>lf_34</t>
-        </is>
-      </c>
-      <c r="B384" t="n">
-        <v>0.8482038248674112</v>
-      </c>
-      <c r="C384" t="inlineStr"/>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>lf_35</t>
-        </is>
-      </c>
-      <c r="B385" t="n">
-        <v>0.8426726028241478</v>
-      </c>
-      <c r="C385" t="inlineStr"/>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>lf_36</t>
-        </is>
-      </c>
-      <c r="B386" t="n">
-        <v>0.8374319120442096</v>
-      </c>
-      <c r="C386" t="inlineStr"/>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>lf_37</t>
-        </is>
-      </c>
-      <c r="B387" t="n">
-        <v>0.8322451012069937</v>
-      </c>
-      <c r="C387" t="inlineStr"/>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>lf_38</t>
-        </is>
-      </c>
-      <c r="B388" t="n">
-        <v>0.8278373345484747</v>
-      </c>
-      <c r="C388" t="inlineStr"/>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>lf_39</t>
-        </is>
-      </c>
-      <c r="B389" t="n">
-        <v>0.823368311917251</v>
-      </c>
-      <c r="C389" t="inlineStr"/>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>lf_40</t>
-        </is>
-      </c>
-      <c r="B390" t="n">
-        <v>0.819735864035027</v>
-      </c>
-      <c r="C390" t="inlineStr"/>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>lf_41</t>
-        </is>
-      </c>
-      <c r="B391" t="n">
-        <v>0.8156985276449513</v>
-      </c>
-      <c r="C391" t="inlineStr"/>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>lf_42</t>
-        </is>
-      </c>
-      <c r="B392" t="n">
-        <v>0.8115739542779589</v>
-      </c>
-      <c r="C392" t="inlineStr"/>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>lf_43</t>
-        </is>
-      </c>
-      <c r="B393" t="n">
-        <v>0.8066615139515587</v>
-      </c>
-      <c r="C393" t="inlineStr"/>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>lf_44</t>
-        </is>
-      </c>
-      <c r="B394" t="n">
-        <v>0.8012861681712108</v>
-      </c>
-      <c r="C394" t="inlineStr"/>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>lf_45</t>
-        </is>
-      </c>
-      <c r="B395" t="n">
-        <v>0.7957388673047624</v>
-      </c>
-      <c r="C395" t="inlineStr"/>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>lf_46</t>
-        </is>
-      </c>
-      <c r="B396" t="n">
-        <v>0.7922744941502728</v>
-      </c>
-      <c r="C396" t="inlineStr"/>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>lf_47</t>
-        </is>
-      </c>
-      <c r="B397" t="n">
-        <v>0.7888429758089698</v>
-      </c>
-      <c r="C397" t="inlineStr"/>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>lf_48</t>
-        </is>
-      </c>
-      <c r="B398" t="n">
-        <v>0.7849577920662306</v>
-      </c>
-      <c r="C398" t="inlineStr"/>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>lf_49</t>
-        </is>
-      </c>
-      <c r="B399" t="n">
-        <v>0.7787736158799848</v>
-      </c>
-      <c r="C399" t="inlineStr"/>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>lf_50</t>
-        </is>
-      </c>
-      <c r="B400" t="n">
-        <v>0.7726211217323297</v>
-      </c>
-      <c r="C400" t="inlineStr"/>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>lf_51</t>
-        </is>
-      </c>
-      <c r="B401" t="n">
-        <v>0.7674776037932218</v>
-      </c>
-      <c r="C401" t="inlineStr"/>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>lf_52</t>
-        </is>
-      </c>
-      <c r="B402" t="n">
-        <v>0.762452467895686</v>
-      </c>
-      <c r="C402" t="inlineStr"/>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>lf_53</t>
-        </is>
-      </c>
-      <c r="B403" t="n">
-        <v>0.7586972618233472</v>
-      </c>
-      <c r="C403" t="inlineStr"/>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>lf_54</t>
-        </is>
-      </c>
-      <c r="B404" t="n">
-        <v>0.7519741563471531</v>
-      </c>
-      <c r="C404" t="inlineStr"/>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>lf_55</t>
-        </is>
-      </c>
-      <c r="B405" t="n">
-        <v>0.7430828932493059</v>
-      </c>
-      <c r="C405" t="inlineStr"/>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>lf_56</t>
-        </is>
-      </c>
-      <c r="B406" t="n">
-        <v>0.737966815017567</v>
-      </c>
-      <c r="C406" t="inlineStr"/>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>lf_57</t>
-        </is>
-      </c>
-      <c r="B407" t="n">
-        <v>0.734382003114307</v>
-      </c>
-      <c r="C407" t="inlineStr"/>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>lf_58</t>
-        </is>
-      </c>
-      <c r="B408" t="n">
-        <v>0.7287916011069201</v>
-      </c>
-      <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>lf_59</t>
-        </is>
-      </c>
-      <c r="B409" t="n">
-        <v>0.7249654771514693</v>
-      </c>
-      <c r="C409" t="inlineStr"/>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>lf_60</t>
-        </is>
-      </c>
-      <c r="B410" t="n">
-        <v>0.7208577228035333</v>
-      </c>
-      <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>lf_61</t>
-        </is>
-      </c>
-      <c r="B411" t="n">
-        <v>0.7152317661113906</v>
-      </c>
-      <c r="C411" t="inlineStr"/>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>lf_62</t>
-        </is>
-      </c>
-      <c r="B412" t="n">
-        <v>0.7112861935282333</v>
-      </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>lf_63</t>
-        </is>
-      </c>
-      <c r="B413" t="n">
-        <v>0.7076861174910986</v>
-      </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>lf_64</t>
-        </is>
-      </c>
-      <c r="B414" t="n">
-        <v>0.7040218654016975</v>
-      </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>lf_65</t>
-        </is>
-      </c>
-      <c r="B415" t="n">
-        <v>0.700367434502581</v>
-      </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>lf_66</t>
-        </is>
-      </c>
-      <c r="B416" t="n">
-        <v>0.6975183525539173</v>
-      </c>
-      <c r="C416" t="inlineStr"/>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>lf_67</t>
-        </is>
-      </c>
-      <c r="B417" t="n">
-        <v>0.6925769016609515</v>
-      </c>
-      <c r="C417" t="inlineStr"/>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>lf_68</t>
-        </is>
-      </c>
-      <c r="B418" t="n">
-        <v>0.6888158405422543</v>
-      </c>
-      <c r="C418" t="inlineStr"/>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>lf_69</t>
-        </is>
-      </c>
-      <c r="B419" t="n">
-        <v>0.6851510195613136</v>
-      </c>
-      <c r="C419" t="inlineStr"/>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>lf_70</t>
-        </is>
-      </c>
-      <c r="B420" t="n">
-        <v>0.6817765360656715</v>
-      </c>
-      <c r="C420" t="inlineStr"/>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>lf_71</t>
-        </is>
-      </c>
-      <c r="B421" t="n">
-        <v>0.6780936225812672</v>
-      </c>
-      <c r="C421" t="inlineStr"/>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>lf_72</t>
-        </is>
-      </c>
-      <c r="B422" t="n">
-        <v>0.6737214652101787</v>
-      </c>
-      <c r="C422" t="inlineStr"/>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>lf_73</t>
-        </is>
-      </c>
-      <c r="B423" t="n">
-        <v>0.6702270464289742</v>
-      </c>
-      <c r="C423" t="inlineStr"/>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>lf_74</t>
-        </is>
-      </c>
-      <c r="B424" t="n">
-        <v>0.6665621430599526</v>
-      </c>
-      <c r="C424" t="inlineStr"/>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>lf_75</t>
-        </is>
-      </c>
-      <c r="B425" t="n">
-        <v>0.6630579636349508</v>
-      </c>
-      <c r="C425" t="inlineStr"/>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>lf_76</t>
-        </is>
-      </c>
-      <c r="B426" t="n">
-        <v>0.6603839824254055</v>
-      </c>
-      <c r="C426" t="inlineStr"/>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>lf_77</t>
-        </is>
-      </c>
-      <c r="B427" t="n">
-        <v>0.6575237114401253</v>
-      </c>
-      <c r="C427" t="inlineStr"/>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>lf_78</t>
-        </is>
-      </c>
-      <c r="B428" t="n">
-        <v>0.6542852970630019</v>
-      </c>
-      <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>lf_79</t>
-        </is>
-      </c>
-      <c r="B429" t="n">
-        <v>0.6465490967319966</v>
-      </c>
-      <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>lf_80</t>
-        </is>
-      </c>
-      <c r="B430" t="n">
-        <v>0.6359094329199044</v>
-      </c>
-      <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>lf_81</t>
-        </is>
-      </c>
-      <c r="B431" t="n">
-        <v>0.6303127686136926</v>
-      </c>
-      <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>lf_82</t>
-        </is>
-      </c>
-      <c r="B432" t="n">
-        <v>0.6263925329584491</v>
-      </c>
-      <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>lf_83</t>
-        </is>
-      </c>
-      <c r="B433" t="n">
-        <v>0.6237429046669273</v>
-      </c>
-      <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>lf_84</t>
-        </is>
-      </c>
-      <c r="B434" t="n">
-        <v>0.6211404864876167</v>
-      </c>
-      <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>lf_85</t>
-        </is>
-      </c>
-      <c r="B435" t="n">
-        <v>0.6185122051985634</v>
-      </c>
-      <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>lf_86</t>
-        </is>
-      </c>
-      <c r="B436" t="n">
-        <v>0.615116942167594</v>
-      </c>
-      <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>lf_87</t>
-        </is>
-      </c>
-      <c r="B437" t="n">
-        <v>0.6121288965111962</v>
-      </c>
-      <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>lf_88</t>
-        </is>
-      </c>
-      <c r="B438" t="n">
-        <v>0.5863708659324223</v>
-      </c>
-      <c r="C438" t="inlineStr"/>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>lf_89</t>
-        </is>
-      </c>
-      <c r="B439" t="n">
-        <v>0.5835405150967293</v>
-      </c>
-      <c r="C439" t="inlineStr"/>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>lf_90</t>
-        </is>
-      </c>
-      <c r="B440" t="n">
-        <v>0.5812149962759572</v>
-      </c>
-      <c r="C440" t="inlineStr"/>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>lf_91</t>
-        </is>
-      </c>
-      <c r="B441" t="n">
-        <v>0.5780776382404557</v>
-      </c>
-      <c r="C441" t="inlineStr"/>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>lf_92</t>
-        </is>
-      </c>
-      <c r="B442" t="n">
-        <v>0.5737912670951947</v>
-      </c>
-      <c r="C442" t="inlineStr"/>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>lf_93</t>
-        </is>
-      </c>
-      <c r="B443" t="n">
-        <v>0.569795222879501</v>
-      </c>
-      <c r="C443" t="inlineStr"/>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>lf_94</t>
-        </is>
-      </c>
-      <c r="B444" t="n">
-        <v>0.5652263586162269</v>
-      </c>
-      <c r="C444" t="inlineStr"/>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>lf_95</t>
-        </is>
-      </c>
-      <c r="B445" t="n">
-        <v>0.5600853166790393</v>
-      </c>
-      <c r="C445" t="inlineStr"/>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>lf_96</t>
-        </is>
-      </c>
-      <c r="B446" t="n">
-        <v>0.5555761849822094</v>
-      </c>
-      <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>lf_97</t>
-        </is>
-      </c>
-      <c r="B447" t="n">
-        <v>0.5516343350484283</v>
-      </c>
-      <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>lf_98</t>
-        </is>
-      </c>
-      <c r="B448" t="n">
-        <v>0.5482912561657574</v>
-      </c>
-      <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>lf_99</t>
-        </is>
-      </c>
-      <c r="B449" t="n">
-        <v>0.5455094536524216</v>
-      </c>
-      <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>lf_100</t>
-        </is>
-      </c>
-      <c r="B450" t="n">
-        <v>0.5438323970445875</v>
-      </c>
-      <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>2025-11-29T16:43:39+08:00</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>